--- a/saida_skus/SKU_UTD-029-KIT-6-POTES-1L-VITTAZA.xlsx
+++ b/saida_skus/SKU_UTD-029-KIT-6-POTES-1L-VITTAZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -867,12 +867,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1021,12 +1021,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1098,12 +1098,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1175,12 +1175,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1329,12 +1329,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1406,12 +1406,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1598,8 +1598,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1608,37 +1610,39 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1663,55 +1667,59 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1736,55 +1744,59 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 459,00</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 68,9%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>3</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1809,33 +1821,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 246,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1852,12 +1864,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1882,33 +1894,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1925,12 +1937,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1955,59 +1967,55 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 459,00</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 68,9%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>21,4%</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2032,59 +2040,55 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 306,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 246,2%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2109,7 +2113,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 306,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2118,7 +2122,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2127,15 +2131,15 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2152,12 +2156,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2182,55 +2186,59 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2255,7 +2263,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 153,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2263,47 +2271,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2331,17 +2343,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▲ 53,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2371,12 +2383,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2401,33 +2413,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 360,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2444,12 +2456,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2474,33 +2486,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 153,00</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2517,12 +2529,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2547,33 +2559,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>▲ 73,3%</t>
+          <t>▲ 53,8%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2590,12 +2602,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2620,33 +2632,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 360,00</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▲ 36,4%</t>
+        <v>26</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2663,12 +2675,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2693,33 +2705,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 153,00</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2736,12 +2748,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2766,33 +2778,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 306,00</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 52,6%</t>
+        <v>26</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2809,12 +2821,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2839,33 +2851,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>15</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 36,4%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2882,12 +2894,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2912,7 +2924,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
+          <t>R$ 153,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2921,24 +2933,24 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>▲ 35,7%</t>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2955,12 +2967,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2994,11 +3006,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 55,6%</t>
+        <v>9</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 52,6%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3028,12 +3040,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3063,28 +3075,28 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>19</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3101,12 +3113,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3131,33 +3143,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 277,00</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+        <v>19</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 35,7%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3174,12 +3186,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3204,12 +3216,12 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 139,00</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
@@ -3217,20 +3229,20 @@
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>▲ 7,7%</t>
+          <t>▲ 55,6%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3247,12 +3259,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3277,7 +3289,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 139,00</t>
+          <t>R$ 277,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3286,16 +3298,16 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>▲ 30,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
@@ -3303,7 +3315,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3320,12 +3332,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3353,17 +3365,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3390,8 +3402,227 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>R$ 139,00</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,7%</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>R$ 139,00</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▲ 30,0%</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O39"/>
+  <autoFilter ref="A1:O42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-029-KIT-6-POTES-1L-VITTAZA.xlsx
+++ b/saida_skus/SKU_UTD-029-KIT-6-POTES-1L-VITTAZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -867,12 +867,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1021,12 +1021,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1098,12 +1098,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1175,12 +1175,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1329,12 +1329,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1406,12 +1406,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1637,12 +1637,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1791,14 +1791,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1829,8 +1829,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1839,39 +1841,41 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1897,17 +1901,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1937,14 +1941,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1967,33 +1971,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 459,00</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▼ 68,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2010,14 +2014,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2040,33 +2044,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 459,00</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 246,2%</t>
+        <v>14</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 68,9%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2083,14 +2087,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2118,20 +2122,20 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>45</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 246,2%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
@@ -2139,7 +2143,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2156,14 +2160,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2186,7 +2190,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 306,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2194,10 +2198,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I23" s="2" t="n">
+        <v>13</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2206,39 +2208,37 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>15,4%</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2310,14 +2310,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2348,8 +2348,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2358,39 +2360,41 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2416,17 +2420,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2456,14 +2460,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2486,33 +2490,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 153,00</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2529,14 +2533,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2559,33 +2563,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 153,00</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 53,8%</t>
+        <v>30</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2602,14 +2606,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2632,33 +2636,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 360,00</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>40</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▲ 53,8%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2675,14 +2679,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2705,33 +2709,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 360,00</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>26</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2748,14 +2752,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2778,33 +2782,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▲ 73,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2821,14 +2825,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2851,33 +2855,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 306,00</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>▲ 36,4%</t>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2894,14 +2898,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2924,33 +2928,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 153,00</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>▲ 22,2%</t>
+          <t>▲ 36,4%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2967,14 +2971,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2997,33 +3001,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 153,00</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 52,6%</t>
+        <v>11</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3040,14 +3044,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3070,33 +3074,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>9</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 52,6%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3113,14 +3117,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3148,15 +3152,15 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 35,7%</t>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3186,14 +3190,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3216,33 +3220,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 277,00</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>▲ 55,6%</t>
+          <t>▲ 35,7%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3259,14 +3263,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3289,33 +3293,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 55,6%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3332,14 +3336,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3362,33 +3366,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 277,00</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+        <v>9</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3405,14 +3409,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3435,33 +3439,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 139,00</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 7,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3478,14 +3482,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3513,20 +3517,20 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>▲ 30,0%</t>
+          <t>▲ 7,7%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
@@ -3534,7 +3538,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3551,78 +3555,151 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>R$ 139,00</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 30,0%</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>UTD-029</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Kit 6 Potes 1L vittaza</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>6482775916</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>R$ 178,35</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="n">
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L42" s="2" t="n">
+      <c r="L43" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M42" s="2" t="inlineStr">
+      <c r="M43" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="N42" s="2" t="inlineStr">
+      <c r="N43" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O42" s="2" t="inlineStr">
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O42"/>
+  <autoFilter ref="A1:O43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-029-KIT-6-POTES-1L-VITTAZA.xlsx
+++ b/saida_skus/SKU_UTD-029-KIT-6-POTES-1L-VITTAZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 357,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -597,51 +597,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I2" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>6,3%</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -666,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -674,51 +670,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I3" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1500,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -743,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -751,10 +743,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -763,39 +753,37 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -867,12 +855,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -944,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1021,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1098,12 +1086,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1175,12 +1163,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1252,12 +1240,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1329,12 +1317,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1406,12 +1394,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1483,12 +1471,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1560,12 +1548,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1637,12 +1625,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1714,12 +1702,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1791,12 +1779,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1868,12 +1856,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1898,7 +1886,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1906,8 +1894,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="n">
-        <v>0</v>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1916,37 +1906,39 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1971,55 +1963,59 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2044,55 +2040,59 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 459,00</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 68,9%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>3</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2117,33 +2117,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 246,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2190,33 +2190,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2263,59 +2263,55 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 459,00</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 68,9%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>21,4%</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2340,59 +2336,55 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 306,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▲ 246,2%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2417,7 +2409,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 306,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2426,7 +2418,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2435,15 +2427,15 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2460,12 +2452,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2490,55 +2482,59 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2563,7 +2559,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 153,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2571,47 +2567,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2639,17 +2639,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▲ 53,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2709,33 +2709,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 360,00</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2782,33 +2782,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 153,00</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>30</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2855,33 +2855,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 73,3%</t>
+        <v>40</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▲ 53,8%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2898,12 +2898,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2928,33 +2928,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 360,00</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▲ 36,4%</t>
+        <v>26</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3001,33 +3001,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 153,00</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>▲ 22,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3074,33 +3074,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 306,00</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>▼ 52,6%</t>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3117,12 +3117,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3147,33 +3147,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>15</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▲ 36,4%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3190,12 +3190,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
+          <t>R$ 153,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3229,24 +3229,24 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▲ 35,7%</t>
+        <v>11</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3296,17 +3296,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>▲ 55,6%</t>
+          <t>▼ 52,6%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3371,28 +3371,28 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>19</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3409,12 +3409,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3439,33 +3439,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 277,00</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,1%</t>
+          <t>▲ 35,7%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3482,12 +3482,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3512,33 +3512,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 139,00</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▲ 7,7%</t>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▲ 55,6%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 139,00</t>
+          <t>R$ 277,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3594,16 +3594,16 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 30,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3661,17 +3661,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3698,8 +3698,227 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>R$ 139,00</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▲ 7,7%</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>R$ 139,00</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▲ 30,0%</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O43"/>
+  <autoFilter ref="A1:O46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-029-KIT-6-POTES-1L-VITTAZA.xlsx
+++ b/saida_skus/SKU_UTD-029-KIT-6-POTES-1L-VITTAZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 357,00</t>
+          <t>R$ 178,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 110,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 178,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -671,24 +671,24 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▲ 1500,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -738,17 +738,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 357,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -816,51 +816,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I5" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>6,3%</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -885,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -893,51 +889,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I6" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1500,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -962,7 +954,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -970,10 +962,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I7" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -982,39 +972,37 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1086,12 +1074,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1163,12 +1151,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1240,12 +1228,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1317,12 +1305,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1394,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1471,12 +1459,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1548,12 +1536,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1625,12 +1613,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1702,12 +1690,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1779,12 +1767,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1856,12 +1844,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1933,12 +1921,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2010,12 +1998,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2087,12 +2075,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2117,7 +2105,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2125,8 +2113,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2135,37 +2125,39 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2190,55 +2182,59 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2263,55 +2259,59 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 459,00</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▼ 68,9%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>3</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2336,33 +2336,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▲ 246,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2379,12 +2379,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2409,33 +2409,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2482,59 +2482,55 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 459,00</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▼ 68,9%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>21,4%</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2559,59 +2555,55 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 306,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▲ 246,2%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2636,7 +2628,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 306,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2645,7 +2637,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2654,15 +2646,15 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2679,12 +2671,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2709,55 +2701,59 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2782,7 +2778,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 153,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2790,47 +2786,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2858,17 +2858,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▲ 53,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2898,12 +2898,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2928,33 +2928,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 360,00</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3001,33 +3001,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 153,00</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3074,33 +3074,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>▲ 73,3%</t>
+          <t>▲ 53,8%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3117,12 +3117,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3147,33 +3147,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 360,00</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▲ 36,4%</t>
+        <v>26</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3190,12 +3190,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3220,33 +3220,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 153,00</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3293,33 +3293,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 306,00</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▼ 52,6%</t>
+        <v>26</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3366,33 +3366,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>15</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▲ 36,4%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3409,12 +3409,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
+          <t>R$ 153,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3448,24 +3448,24 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>▲ 35,7%</t>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3482,12 +3482,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3521,11 +3521,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▲ 55,6%</t>
+        <v>9</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▼ 52,6%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3590,28 +3590,28 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>19</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3658,33 +3658,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 277,00</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+        <v>19</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▲ 35,7%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3731,12 +3731,12 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 139,00</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
@@ -3744,20 +3744,20 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>▲ 7,7%</t>
+          <t>▲ 55,6%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3774,12 +3774,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 139,00</t>
+          <t>R$ 277,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3813,16 +3813,16 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>▲ 30,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3880,17 +3880,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3917,8 +3917,227 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>R$ 139,00</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▲ 7,7%</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>R$ 139,00</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▲ 30,0%</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O46"/>
+  <autoFilter ref="A1:O49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-029-KIT-6-POTES-1L-VITTAZA.xlsx
+++ b/saida_skus/SKU_UTD-029-KIT-6-POTES-1L-VITTAZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -589,25 +589,25 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 178,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 321,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▲ 80,3%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▲ 110,0%</t>
+        <v>19</v>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>▼ 9,5%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
@@ -615,7 +615,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -667,20 +667,20 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>21</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▲ 110,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 178,00</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 357,00</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -881,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 357,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -890,24 +890,24 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>▲ 1500,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>16</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1500,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1035,10 +1035,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I8" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1047,39 +1045,37 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1151,12 +1147,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1228,12 +1224,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1305,12 +1301,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1382,12 +1378,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,12 +1455,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1536,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1613,12 +1609,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1690,12 +1686,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1767,12 +1763,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1844,12 +1840,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1921,12 +1917,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1998,12 +1994,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2075,12 +2071,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2152,12 +2148,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2229,12 +2225,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2306,14 +2302,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2336,7 +2332,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2344,8 +2340,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2354,39 +2352,41 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2412,17 +2412,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2452,14 +2452,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2482,33 +2482,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 459,00</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>▼ 68,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2525,14 +2525,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2555,33 +2555,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 459,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▲ 246,2%</t>
+        <v>14</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▼ 68,9%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2598,14 +2598,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2633,20 +2633,20 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>45</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▲ 246,2%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2671,14 +2671,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 306,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2709,10 +2709,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I30" s="2" t="n">
+        <v>13</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2721,39 +2719,37 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>15,4%</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2825,14 +2821,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2855,7 +2851,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2863,8 +2859,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="n">
-        <v>0</v>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2873,39 +2871,41 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2931,17 +2931,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2971,14 +2971,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3001,33 +3001,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 153,00</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3044,14 +3044,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3074,33 +3074,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 153,00</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▲ 53,8%</t>
+        <v>30</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3117,14 +3117,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3147,33 +3147,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 360,00</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>40</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▲ 53,8%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3190,14 +3190,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3220,33 +3220,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 360,00</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>26</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3263,14 +3263,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3293,33 +3293,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▲ 73,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3336,14 +3336,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3366,33 +3366,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 306,00</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>▲ 36,4%</t>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3409,14 +3409,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3439,33 +3439,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 153,00</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>▲ 22,2%</t>
+          <t>▲ 36,4%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3482,14 +3482,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3512,33 +3512,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 153,00</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▼ 52,6%</t>
+        <v>11</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3555,14 +3555,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3585,33 +3585,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>9</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 52,6%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3628,14 +3628,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3663,15 +3663,15 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▲ 35,7%</t>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3701,14 +3701,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3731,33 +3731,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 277,00</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>▲ 55,6%</t>
+          <t>▲ 35,7%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3774,14 +3774,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3804,33 +3804,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 55,6%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3847,14 +3847,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3877,33 +3877,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 277,00</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+        <v>9</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3920,14 +3920,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3950,33 +3950,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 139,00</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▲ 7,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3993,14 +3993,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -4028,20 +4028,20 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▲ 30,0%</t>
+          <t>▲ 7,7%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4066,78 +4066,151 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>R$ 139,00</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▲ 30,0%</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>UTD-029</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Kit 6 Potes 1L vittaza</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>6482775916</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>R$ 178,35</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="n">
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L49" s="2" t="n">
+      <c r="L50" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M49" s="2" t="inlineStr">
+      <c r="M50" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="N49" s="2" t="inlineStr">
+      <c r="N50" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O49" s="2" t="inlineStr">
+      <c r="O50" s="2" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O49"/>
+  <autoFilter ref="A1:O50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-029-KIT-6-POTES-1L-VITTAZA.xlsx
+++ b/saida_skus/SKU_UTD-029-KIT-6-POTES-1L-VITTAZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 321,00</t>
+          <t>R$ 482,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▲ 80,3%</t>
+          <t>▲ 199,4%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>▼ 9,5%</t>
+        <v>22</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,25 +662,25 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 178,00</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 161,00</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>▼ 49,8%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▲ 110,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,8%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
@@ -688,7 +688,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,25 +735,25 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 178,00</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 321,00</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>▲ 80,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>19</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 9,5%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
@@ -761,7 +761,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 178,00</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>21</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▲ 110,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 357,00</t>
+          <t>R$ 178,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -890,24 +890,24 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -957,17 +957,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▲ 1500,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 357,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1036,24 +1036,24 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>32</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1108,51 +1108,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I9" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1500,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1177,7 +1173,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1185,10 +1181,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I10" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1197,39 +1191,37 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1301,12 +1293,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1378,12 +1370,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1455,12 +1447,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1532,12 +1524,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,12 +1601,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1686,12 +1678,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1763,12 +1755,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1840,12 +1832,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1917,12 +1909,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1994,12 +1986,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2071,12 +2063,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2148,12 +2140,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2225,12 +2217,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2302,12 +2294,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2379,12 +2371,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2409,7 +2401,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2417,8 +2409,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2427,37 +2421,39 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2482,55 +2478,59 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2555,33 +2555,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 459,00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▼ 68,9%</t>
+        <v>0</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2628,33 +2628,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▲ 246,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2671,12 +2671,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2701,33 +2701,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 459,00</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>14</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▼ 68,9%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2774,59 +2774,55 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 306,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▲ 246,2%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2851,7 +2847,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 306,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2859,10 +2855,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I32" s="2" t="n">
+        <v>13</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2871,39 +2865,37 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>15,4%</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2928,7 +2920,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2936,8 +2928,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="n">
-        <v>0</v>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2946,37 +2940,39 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3001,55 +2997,59 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 153,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3083,24 +3083,24 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3117,12 +3117,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3156,11 +3156,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▲ 53,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3190,12 +3190,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 360,00</t>
+          <t>R$ 153,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3229,16 +3229,16 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>30</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3302,11 +3302,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>40</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▲ 53,8%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
+          <t>R$ 360,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3377,22 +3377,22 @@
       <c r="I39" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▲ 73,3%</t>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3409,12 +3409,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3448,11 +3448,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▲ 36,4%</t>
+        <v>0</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3482,12 +3482,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 153,00</t>
+          <t>R$ 306,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3521,24 +3521,24 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>▲ 22,2%</t>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3594,11 +3594,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▼ 52,6%</t>
+        <v>15</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▲ 36,4%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3658,33 +3658,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
+          <t>R$ 153,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>11</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3731,33 +3731,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▲ 35,7%</t>
+        <v>9</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▼ 52,6%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3774,12 +3774,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3804,33 +3804,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 277,00</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▲ 55,6%</t>
+        <v>19</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3886,24 +3886,24 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 35,7%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3920,12 +3920,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3959,11 +3959,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+        <v>14</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▲ 55,6%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4023,25 +4023,25 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 139,00</t>
+          <t>R$ 277,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▲ 7,7%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4096,33 +4096,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 139,00</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▲ 30,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4139,78 +4139,224 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>R$ 139,00</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▲ 7,7%</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>R$ 139,00</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▲ 30,0%</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>UTD-029</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Kit 6 Potes 1L vittaza</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>6482775916</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>R$ 178,35</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="n">
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L50" s="2" t="n">
+      <c r="L52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M50" s="2" t="inlineStr">
+      <c r="M52" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="N50" s="2" t="inlineStr">
+      <c r="N52" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O50" s="2" t="inlineStr">
+      <c r="O52" s="2" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O50"/>
+  <autoFilter ref="A1:O52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-029-KIT-6-POTES-1L-VITTAZA.xlsx
+++ b/saida_skus/SKU_UTD-029-KIT-6-POTES-1L-VITTAZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:O64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -594,28 +594,28 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▲ 199,4%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▲ 37,5%</t>
+          <t>▼ 67,6%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 161,00</t>
+          <t>R$ 803,00</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>▼ 49,8%</t>
+          <t>▲ 66,6%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,8%</t>
+          <t>▲ 7,6%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 321,00</t>
+          <t>R$ 482,00</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>▲ 80,3%</t>
+          <t>▼ 24,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>▼ 9,5%</t>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 178,00</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 642,00</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 298,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>▲ 110,0%</t>
+          <t>▼ 2,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,25 +881,25 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 178,00</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 161,00</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>49</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
@@ -907,7 +907,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 1.124,00</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>33</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,9%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 357,00</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 803,00</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 17,1%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 321,00</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,4%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>▲ 1500,0%</t>
+          <t>▼ 22,6%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 161,00</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 43,2%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,59 +1246,55 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 321,00</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,4%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 54,2%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>5,4%</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1323,7 +1319,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 161,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1331,51 +1327,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I12" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1400,59 +1392,55 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,1%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1477,59 +1465,55 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 482,00</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 199,4%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1554,59 +1538,55 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 161,00</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,8%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,8%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>6,3%</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1631,59 +1611,55 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 321,00</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 80,3%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,5%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1708,59 +1684,55 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 178,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▲ 110,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1785,7 +1757,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 178,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1793,10 +1765,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I18" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1805,39 +1775,37 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1862,59 +1830,55 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1939,7 +1903,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 357,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1947,51 +1911,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I20" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>6,3%</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2016,7 +1976,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2024,51 +1984,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I21" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1500,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2093,7 +2049,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2101,10 +2057,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I22" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2113,39 +2067,37 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2217,12 +2169,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2294,12 +2246,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2371,12 +2323,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2448,12 +2400,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2525,12 +2477,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2555,7 +2507,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2563,8 +2515,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n">
-        <v>0</v>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2573,37 +2527,39 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2628,55 +2584,59 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2701,55 +2661,59 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 459,00</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 68,9%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>3</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2774,55 +2738,59 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▲ 246,2%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2847,7 +2815,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2855,8 +2823,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="n">
-        <v>13</v>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2865,37 +2835,39 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2967,12 +2939,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3044,12 +3016,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3074,7 +3046,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3082,8 +3054,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n">
-        <v>0</v>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3092,37 +3066,39 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3147,55 +3123,59 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3220,7 +3200,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 153,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3228,47 +3208,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3293,55 +3277,59 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▲ 53,8%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3366,7 +3354,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 360,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3374,8 +3362,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="n">
-        <v>26</v>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3384,37 +3374,39 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3442,17 +3434,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3482,12 +3474,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3512,33 +3504,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>▲ 73,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3555,12 +3547,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3585,33 +3577,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 459,00</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>▲ 36,4%</t>
+          <t>▼ 68,9%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3628,12 +3620,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3658,33 +3650,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 153,00</t>
+          <t>R$ 306,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
+        <v>45</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>▲ 246,2%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3701,12 +3693,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3731,33 +3723,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 306,00</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▼ 52,6%</t>
+        <v>13</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3774,12 +3766,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3804,55 +3796,59 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>19</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3877,7 +3873,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3885,47 +3881,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▲ 35,7%</t>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3953,17 +3953,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▲ 55,6%</t>
+        <v>0</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4023,33 +4023,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4096,33 +4096,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 153,00</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+        <v>30</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4169,33 +4169,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 139,00</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▲ 7,7%</t>
+        <v>40</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 53,8%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 139,00</t>
+          <t>R$ 360,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4251,16 +4251,16 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▲ 30,0%</t>
+        <v>26</v>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4318,17 +4318,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4355,8 +4355,884 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>R$ 306,00</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>▲ 73,3%</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 36,4%</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>R$ 153,00</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 52,6%</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>R$ 277,00</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>10,5%</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>R$ 277,00</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 35,7%</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>10,5%</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▲ 55,6%</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>R$ 277,00</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>R$ 139,00</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,7%</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>R$ 139,00</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>▲ 30,0%</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O52"/>
+  <autoFilter ref="A1:O64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-029-KIT-6-POTES-1L-VITTAZA.xlsx
+++ b/saida_skus/SKU_UTD-029-KIT-6-POTES-1L-VITTAZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O64"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 482,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 67,6%</t>
+          <t>▼ 37,3%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 803,00</t>
+          <t>R$ 645,00</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,6%</t>
+          <t>▲ 93,1%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>▲ 7,6%</t>
+          <t>▲ 26,4%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 482,00</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,9%</t>
+          <t>R$ 334,00</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 37,5%</t>
+        <v>53</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 642,00</t>
+          <t>R$ 334,00</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>▲ 298,8%</t>
+          <t>▲ 7,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 161,00</t>
+          <t>R$ 311,00</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>▼ 85,7%</t>
+          <t>▼ 33,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>▲ 48,5%</t>
+          <t>▲ 13,3%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.124,00</t>
+          <t>R$ 467,00</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>▲ 40,0%</t>
+          <t>▲ 50,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,9%</t>
+          <t>▼ 26,8%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 803,00</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,2%</t>
+          <t>R$ 311,00</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 51,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 17,1%</t>
+        <v>82</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,3%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 321,00</t>
+          <t>R$ 645,00</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>▲ 99,4%</t>
+          <t>▲ 313,5%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,6%</t>
+        <v>75</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2,7%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,25 +1173,25 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 161,00</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,8%</t>
+          <t>R$ 156,00</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>▲ 43,2%</t>
+          <t>▲ 35,2%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 321,00</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>▲ 99,4%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>▲ 54,2%</t>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,25 +1319,25 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 161,00</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 156,00</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 166,7%</t>
+        <v>51</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,9%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 934,00</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,1%</t>
+        <v>56</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,7%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 482,00</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 199,4%</t>
+          <t>R$ 467,00</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▲ 37,5%</t>
+          <t>▲ 32,5%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 161,00</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,8%</t>
+          <t>R$ 490,00</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 214,1%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,8%</t>
+        <v>40</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 81,8%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,25 +1611,25 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 321,00</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 80,3%</t>
+          <t>R$ 156,00</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 51,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,5%</t>
+        <v>22</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,8%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 178,00</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 321,00</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▲ 110,0%</t>
+        <v>19</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 51,3%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,25 +1757,25 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 178,00</t>
+          <t>R$ 161,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>39</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 85,7%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 161,00</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>21</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 357,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1912,24 +1912,24 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1500,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2052,17 +2052,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 95,7%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2122,59 +2122,55 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 482,00</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 67,6%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>13,0%</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2199,59 +2195,55 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 803,00</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,6%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,6%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>7,0%</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2276,59 +2268,55 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 482,00</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,9%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>4,5%</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2353,59 +2341,55 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 642,00</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 298,8%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>6,3%</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2430,59 +2414,55 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 161,00</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,7%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2507,59 +2487,55 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 1.124,00</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,9%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>21,2%</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2584,59 +2560,55 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 803,00</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,2%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 17,1%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>11,8%</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2661,59 +2633,55 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 321,00</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,4%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,6%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2738,59 +2706,55 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 161,00</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,8%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▲ 43,2%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2815,59 +2779,55 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 321,00</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,4%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 54,2%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>5,4%</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2892,7 +2852,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 161,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2900,51 +2860,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I33" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2969,59 +2925,55 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,1%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3046,59 +2998,55 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 482,00</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>▲ 199,4%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3123,59 +3071,55 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 161,00</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,8%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,8%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>6,3%</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3200,59 +3144,55 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 321,00</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>▲ 80,3%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,5%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3277,59 +3217,55 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 178,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 110,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3354,7 +3290,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 178,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3362,10 +3298,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I39" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3374,39 +3308,37 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3434,17 +3366,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3467,19 +3399,19 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3504,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 357,00</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>32</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3540,19 +3472,19 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3577,33 +3509,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 459,00</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 68,9%</t>
+        <v>16</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1500,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3613,19 +3545,19 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3650,33 +3582,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>▲ 246,2%</t>
+        <v>1</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3686,19 +3618,19 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3723,7 +3655,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3731,8 +3663,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="2" t="n">
-        <v>13</v>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3741,37 +3675,39 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3843,12 +3779,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3920,12 +3856,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3950,7 +3886,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3958,8 +3894,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n">
-        <v>0</v>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -3968,37 +3906,39 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4023,55 +3963,59 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4096,7 +4040,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 153,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4104,47 +4048,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4169,55 +4117,59 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 53,8%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4242,7 +4194,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 360,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4250,8 +4202,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
-        <v>26</v>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4260,37 +4214,39 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4315,55 +4271,59 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4388,7 +4348,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4396,47 +4356,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>▲ 73,3%</t>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4461,55 +4425,59 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 36,4%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4534,7 +4502,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 153,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4542,47 +4510,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4607,55 +4579,59 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 52,6%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4680,55 +4656,59 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="n">
-        <v>19</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4753,7 +4733,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4761,47 +4741,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I58" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 35,7%</t>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4826,55 +4810,59 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▲ 55,6%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4899,7 +4887,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4907,47 +4895,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4975,17 +4967,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+        <v>0</v>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -5015,12 +5007,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5045,33 +5037,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 139,00</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 7,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5088,12 +5080,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5118,33 +5110,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 139,00</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 459,00</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>▲ 30,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 68,9%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5161,78 +5153,1619 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>R$ 306,00</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 246,2%</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>R$ 306,00</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>15,4%</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>R$ 153,00</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▲ 53,8%</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>R$ 360,00</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>R$ 306,00</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 73,3%</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 36,4%</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>R$ 153,00</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 52,6%</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 277,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>10,5%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 277,00</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>▲ 35,7%</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>10,5%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 55,6%</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 277,00</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 139,00</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,7%</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 139,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 30,0%</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>UTD-029</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Kit 6 Potes 1L vittaza</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>6482775916</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>R$ 178,35</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="n">
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L64" s="2" t="n">
+      <c r="L85" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M64" s="2" t="inlineStr">
+      <c r="M85" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="N64" s="2" t="inlineStr">
+      <c r="N85" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O64" s="2" t="inlineStr">
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O64"/>
+  <autoFilter ref="A1:O85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-029-KIT-6-POTES-1L-VITTAZA.xlsx
+++ b/saida_skus/SKU_UTD-029-KIT-6-POTES-1L-VITTAZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$86</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 334,00</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 37,3%</t>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 645,00</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>▲ 93,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>▲ 26,4%</t>
+        <v>42</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,3%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 334,00</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 645,00</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 93,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>67</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26,4%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -811,22 +811,22 @@
           <t>R$ 334,00</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 7,4%</t>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>53</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
@@ -834,7 +834,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -881,25 +881,25 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 311,00</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,4%</t>
+          <t>R$ 334,00</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 13,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
@@ -907,7 +907,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -954,25 +954,25 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,2%</t>
+          <t>R$ 311,00</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 26,8%</t>
+        <v>68</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▲ 13,3%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1027,25 +1027,25 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 311,00</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 51,8%</t>
+          <t>R$ 467,00</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,3%</t>
+        <v>60</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,8%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 645,00</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 313,5%</t>
+          <t>R$ 311,00</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 51,8%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>▲ 2,7%</t>
+          <t>▲ 9,3%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 645,00</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 313,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>▲ 35,2%</t>
+          <t>▲ 2,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 156,00</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>▲ 5,9%</t>
+          <t>▲ 35,2%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>▼ 83,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,9%</t>
+        <v>54</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 934,00</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 156,00</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,7%</t>
+        <v>51</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,9%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,7%</t>
+          <t>R$ 934,00</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▲ 32,5%</t>
+          <t>▲ 5,7%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1538,25 +1538,25 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 490,00</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>▲ 214,1%</t>
+          <t>R$ 467,00</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,7%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>▲ 81,8%</t>
+          <t>▲ 32,5%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 51,4%</t>
+          <t>R$ 490,00</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 214,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>▲ 15,8%</t>
+          <t>▲ 81,8%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,14 +1654,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 321,00</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>▲ 99,4%</t>
+          <t>R$ 156,00</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 51,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 51,3%</t>
+        <v>22</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,8%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,14 +1727,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 161,00</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 321,00</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 85,7%</t>
+        <v>19</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 51,3%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,14 +1800,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1835,20 +1835,20 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>39</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 85,7%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,14 +1873,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 161,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1921,15 +1921,15 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1987,9 +1987,9 @@
       <c r="I21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2019,14 +2019,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2052,17 +2052,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 95,7%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2092,14 +2092,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 482,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>▼ 67,6%</t>
+          <t>▼ 95,7%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,14 +2165,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 803,00</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,6%</t>
+          <t>R$ 482,00</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 7,6%</t>
+        <v>23</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 67,6%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,14 +2238,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 482,00</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,9%</t>
+          <t>R$ 803,00</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>▲ 37,5%</t>
+          <t>▲ 7,6%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,14 +2311,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2341,25 +2341,25 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 642,00</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 298,8%</t>
+          <t>R$ 482,00</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 2,0%</t>
+        <v>66</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,14 +2384,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 161,00</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 85,7%</t>
+          <t>R$ 642,00</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>▲ 298,8%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 48,5%</t>
+        <v>48</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,14 +2457,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2487,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.124,00</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+          <t>R$ 161,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 2,9%</t>
+        <v>49</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,14 +2530,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 803,00</t>
+          <t>R$ 1.124,00</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,2%</t>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>▼ 17,1%</t>
+          <t>▼ 2,9%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,14 +2603,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2633,33 +2633,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 321,00</t>
+          <t>R$ 803,00</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>▲ 99,4%</t>
+          <t>▲ 150,2%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>▼ 22,6%</t>
+          <t>▼ 17,1%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,14 +2676,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2706,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 161,00</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,8%</t>
+          <t>R$ 321,00</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,4%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▲ 43,2%</t>
+        <v>41</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,6%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,14 +2749,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2779,33 +2779,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 321,00</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 99,4%</t>
+          <t>R$ 161,00</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,8%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>▲ 54,2%</t>
+          <t>▲ 43,2%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,14 +2822,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2852,33 +2852,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 161,00</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 321,00</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,4%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>▲ 166,7%</t>
+          <t>▲ 54,2%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,14 +2895,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2925,33 +2925,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 161,00</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,1%</t>
+        <v>24</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,14 +2968,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 482,00</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>▲ 199,4%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▲ 37,5%</t>
+        <v>9</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,1%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,14 +3041,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3071,33 +3071,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 161,00</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,8%</t>
+          <t>R$ 482,00</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 199,4%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,8%</t>
+        <v>22</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,14 +3114,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3144,25 +3144,25 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 321,00</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>▲ 80,3%</t>
+          <t>R$ 161,00</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,8%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>▼ 9,5%</t>
+          <t>▼ 15,8%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,14 +3187,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3217,25 +3217,25 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 178,00</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 321,00</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 80,3%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 110,0%</t>
+        <v>19</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,5%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,14 +3260,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3295,20 +3295,20 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>21</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 110,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
@@ -3333,14 +3333,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3363,33 +3363,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 178,00</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,14 +3406,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3436,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 357,00</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,14 +3479,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 357,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3518,24 +3518,24 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>▲ 1500,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3552,14 +3552,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3591,11 +3591,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>16</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1500,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3625,14 +3625,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3663,10 +3663,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I44" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3675,39 +3673,37 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3779,12 +3775,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3856,12 +3852,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3933,12 +3929,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4010,12 +4006,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4087,12 +4083,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4164,12 +4160,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4241,12 +4237,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4318,12 +4314,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4395,12 +4391,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4472,12 +4468,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4549,12 +4545,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4626,12 +4622,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4703,12 +4699,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4780,12 +4776,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4857,12 +4853,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4934,14 +4930,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -4964,7 +4960,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4972,8 +4968,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>0</v>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -4982,39 +4980,41 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5040,17 +5040,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5080,14 +5080,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5110,33 +5110,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 459,00</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>▼ 68,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5153,14 +5153,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5183,33 +5183,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 459,00</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 246,2%</t>
+        <v>14</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 68,9%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5226,14 +5226,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5261,20 +5261,20 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>45</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▲ 246,2%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5299,14 +5299,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 306,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5337,10 +5337,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I66" s="2" t="n">
+        <v>13</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5349,39 +5347,37 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>15,4%</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5453,14 +5449,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5483,7 +5479,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5491,8 +5487,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n">
-        <v>0</v>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5501,39 +5499,41 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5559,17 +5559,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5599,14 +5599,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5629,33 +5629,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 153,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5672,14 +5672,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5702,33 +5702,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 153,00</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▲ 53,8%</t>
+        <v>30</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5745,14 +5745,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5775,33 +5775,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 360,00</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>40</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 53,8%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5818,14 +5818,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5848,33 +5848,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 360,00</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>26</v>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5891,14 +5891,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5921,33 +5921,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 73,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5964,14 +5964,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5994,33 +5994,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 306,00</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>▲ 36,4%</t>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -6037,14 +6037,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -6067,33 +6067,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 153,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>▲ 22,2%</t>
+          <t>▲ 36,4%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6110,14 +6110,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -6140,33 +6140,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 153,00</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 52,6%</t>
+        <v>11</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6183,14 +6183,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -6213,33 +6213,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>9</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 52,6%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6256,14 +6256,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -6291,15 +6291,15 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>▲ 35,7%</t>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6329,14 +6329,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -6359,33 +6359,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 277,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>▲ 55,6%</t>
+          <t>▲ 35,7%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6402,14 +6402,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -6432,33 +6432,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 55,6%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6475,14 +6475,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -6505,33 +6505,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 277,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+        <v>9</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6548,14 +6548,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -6578,33 +6578,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 139,00</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>▲ 7,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6621,14 +6621,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -6656,20 +6656,20 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>▲ 30,0%</t>
+          <t>▲ 7,7%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6694,78 +6694,151 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 139,00</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>▲ 30,0%</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>UTD-029</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Kit 6 Potes 1L vittaza</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>6482775916</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>R$ 178,35</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="n">
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L85" s="2" t="n">
+      <c r="L86" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M85" s="2" t="inlineStr">
+      <c r="M86" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="N85" s="2" t="inlineStr">
+      <c r="N86" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O85" s="2" t="inlineStr">
+      <c r="O86" s="2" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O85"/>
+  <autoFilter ref="A1:O86"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-029-KIT-6-POTES-1L-VITTAZA.xlsx
+++ b/saida_skus/SKU_UTD-029-KIT-6-POTES-1L-VITTAZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$87</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O86"/>
+  <dimension ref="A1:O87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -589,25 +589,25 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 334,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 311,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>33</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
@@ -615,7 +615,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 334,00</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 37,3%</t>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 645,00</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 93,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 26,4%</t>
+        <v>42</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,3%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 334,00</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 645,00</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 93,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>67</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26,4%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -884,22 +884,22 @@
           <t>R$ 334,00</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 7,4%</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>53</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
@@ -907,7 +907,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -954,25 +954,25 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 311,00</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,4%</t>
+          <t>R$ 334,00</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>▲ 13,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1027,25 +1027,25 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,2%</t>
+          <t>R$ 311,00</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 26,8%</t>
+        <v>68</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 13,3%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1100,25 +1100,25 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 311,00</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 51,8%</t>
+          <t>R$ 467,00</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,2%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,3%</t>
+        <v>60</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,8%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 645,00</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 313,5%</t>
+          <t>R$ 311,00</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 51,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>▲ 2,7%</t>
+          <t>▲ 9,3%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 645,00</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 313,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>▲ 35,2%</t>
+          <t>▲ 2,7%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 156,00</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▲ 5,9%</t>
+          <t>▲ 35,2%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>▼ 83,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,9%</t>
+        <v>54</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 934,00</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 156,00</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,7%</t>
+        <v>51</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,9%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,7%</t>
+          <t>R$ 934,00</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>▲ 32,5%</t>
+          <t>▲ 5,7%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1611,25 +1611,25 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 490,00</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 214,1%</t>
+          <t>R$ 467,00</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>▲ 81,8%</t>
+          <t>▲ 32,5%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,14 +1654,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 51,4%</t>
+          <t>R$ 490,00</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>▲ 214,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>▲ 15,8%</t>
+          <t>▲ 81,8%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,14 +1727,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 321,00</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 99,4%</t>
+          <t>R$ 156,00</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 51,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 51,3%</t>
+        <v>22</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,8%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,14 +1800,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 161,00</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 321,00</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>▲ 85,7%</t>
+        <v>19</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 51,3%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,14 +1873,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1908,20 +1908,20 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>39</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 85,7%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,14 +1946,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 161,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -1994,15 +1994,15 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2060,9 +2060,9 @@
       <c r="I22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2092,14 +2092,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2125,17 +2125,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 95,7%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2165,14 +2165,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 482,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>▼ 67,6%</t>
+          <t>▼ 95,7%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,14 +2238,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 803,00</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,6%</t>
+          <t>R$ 482,00</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▲ 7,6%</t>
+        <v>23</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 67,6%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,14 +2311,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 482,00</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,9%</t>
+          <t>R$ 803,00</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▲ 37,5%</t>
+          <t>▲ 7,6%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,14 +2384,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2414,25 +2414,25 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 642,00</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 298,8%</t>
+          <t>R$ 482,00</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,9%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 2,0%</t>
+        <v>66</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,14 +2457,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2487,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 161,00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 85,7%</t>
+          <t>R$ 642,00</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 298,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 48,5%</t>
+        <v>48</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,14 +2530,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.124,00</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+          <t>R$ 161,00</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 2,9%</t>
+        <v>49</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,14 +2603,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2633,33 +2633,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 803,00</t>
+          <t>R$ 1.124,00</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,2%</t>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>▼ 17,1%</t>
+          <t>▼ 2,9%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,14 +2676,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2706,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 321,00</t>
+          <t>R$ 803,00</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>▲ 99,4%</t>
+          <t>▲ 150,2%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>▼ 22,6%</t>
+          <t>▼ 17,1%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,14 +2749,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2779,33 +2779,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 161,00</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,8%</t>
+          <t>R$ 321,00</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,4%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 43,2%</t>
+        <v>41</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,6%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,14 +2822,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2852,33 +2852,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 321,00</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>▲ 99,4%</t>
+          <t>R$ 161,00</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,8%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>▲ 54,2%</t>
+          <t>▲ 43,2%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,14 +2895,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2925,33 +2925,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 161,00</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 321,00</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,4%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>▲ 166,7%</t>
+          <t>▲ 54,2%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,14 +2968,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 161,00</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,1%</t>
+        <v>24</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,14 +3041,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3071,33 +3071,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 482,00</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 199,4%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 37,5%</t>
+        <v>9</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,1%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,14 +3114,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3144,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 161,00</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,8%</t>
+          <t>R$ 482,00</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>▲ 199,4%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,8%</t>
+        <v>22</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,14 +3187,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3217,25 +3217,25 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 321,00</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 80,3%</t>
+          <t>R$ 161,00</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,8%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>▼ 9,5%</t>
+          <t>▼ 15,8%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,14 +3260,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3290,25 +3290,25 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 178,00</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 321,00</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 80,3%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▲ 110,0%</t>
+        <v>19</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,5%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,14 +3333,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3368,20 +3368,20 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>21</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 110,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
@@ -3406,14 +3406,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3436,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 178,00</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,14 +3479,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3509,33 +3509,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 357,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3552,14 +3552,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 357,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3591,24 +3591,24 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>▲ 1500,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,14 +3625,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3664,11 +3664,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>16</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1500,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3698,14 +3698,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3736,10 +3736,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I45" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3748,39 +3746,37 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3852,12 +3848,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3929,12 +3925,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4006,12 +4002,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4083,12 +4079,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4160,12 +4156,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4237,12 +4233,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4314,12 +4310,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4391,12 +4387,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4468,12 +4464,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4545,12 +4541,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4622,12 +4618,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4699,12 +4695,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4776,12 +4772,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4853,12 +4849,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4930,12 +4926,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5007,14 +5003,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5037,7 +5033,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5045,8 +5041,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I62" s="2" t="n">
-        <v>0</v>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5055,39 +5053,41 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5113,17 +5113,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5153,14 +5153,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5183,33 +5183,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 459,00</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>▼ 68,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5226,14 +5226,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5256,33 +5256,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 459,00</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▲ 246,2%</t>
+        <v>14</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 68,9%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5299,14 +5299,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5334,20 +5334,20 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>45</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 246,2%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5372,14 +5372,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5402,7 +5402,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 306,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5410,10 +5410,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I67" s="2" t="n">
+        <v>13</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5422,39 +5420,37 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>15,4%</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5526,14 +5522,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5556,7 +5552,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5564,8 +5560,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
-        <v>0</v>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5574,39 +5572,41 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5632,17 +5632,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5672,14 +5672,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5702,33 +5702,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 153,00</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5745,14 +5745,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5775,33 +5775,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 153,00</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 53,8%</t>
+        <v>30</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5818,14 +5818,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5848,33 +5848,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 360,00</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>40</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 53,8%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5891,14 +5891,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5921,33 +5921,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 360,00</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>26</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5964,14 +5964,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5994,33 +5994,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▲ 73,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -6037,14 +6037,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -6067,33 +6067,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 306,00</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>▲ 36,4%</t>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6110,14 +6110,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -6140,33 +6140,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 153,00</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>▲ 22,2%</t>
+          <t>▲ 36,4%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6183,14 +6183,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -6213,33 +6213,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 153,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 52,6%</t>
+        <v>11</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6256,14 +6256,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -6286,33 +6286,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>9</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 52,6%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6329,14 +6329,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -6364,15 +6364,15 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 35,7%</t>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6402,14 +6402,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -6432,33 +6432,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 277,00</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>▲ 55,6%</t>
+          <t>▲ 35,7%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6475,14 +6475,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -6505,33 +6505,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 55,6%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6548,14 +6548,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -6578,33 +6578,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 277,00</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+        <v>9</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6621,14 +6621,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -6651,33 +6651,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 139,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 7,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6694,14 +6694,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -6729,20 +6729,20 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>▲ 30,0%</t>
+          <t>▲ 7,7%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6767,78 +6767,151 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 139,00</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 30,0%</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>UTD-029</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>Kit 6 Potes 1L vittaza</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>6482775916</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>R$ 178,35</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="n">
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr">
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L86" s="2" t="n">
+      <c r="L87" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M86" s="2" t="inlineStr">
+      <c r="M87" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="N86" s="2" t="inlineStr">
+      <c r="N87" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O86" s="2" t="inlineStr">
+      <c r="O87" s="2" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O86"/>
+  <autoFilter ref="A1:O87"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-029-KIT-6-POTES-1L-VITTAZA.xlsx
+++ b/saida_skus/SKU_UTD-029-KIT-6-POTES-1L-VITTAZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O87"/>
+  <dimension ref="A1:O88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 311,00</t>
+          <t>R$ 623,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,9%</t>
+          <t>▲ 100,3%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,4%</t>
+          <t>▲ 9,1%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -662,25 +662,25 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 334,00</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 311,00</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>33</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
@@ -688,7 +688,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 334,00</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 37,3%</t>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 645,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>▲ 93,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>▲ 26,4%</t>
+          <t>▼ 37,3%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 334,00</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 645,00</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▲ 93,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>67</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▲ 26,4%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -957,22 +957,22 @@
           <t>R$ 334,00</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>▲ 7,4%</t>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>53</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1027,25 +1027,25 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 311,00</t>
+          <t>R$ 334,00</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,4%</t>
+          <t>▲ 7,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>▲ 13,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1100,25 +1100,25 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
+          <t>R$ 311,00</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,2%</t>
+          <t>▼ 33,4%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>▼ 26,8%</t>
+          <t>▲ 13,3%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1173,25 +1173,25 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 311,00</t>
+          <t>R$ 467,00</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>▼ 51,8%</t>
+          <t>▲ 50,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>▲ 9,3%</t>
+          <t>▼ 26,8%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 645,00</t>
+          <t>R$ 311,00</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>▲ 313,5%</t>
+          <t>▼ 51,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2,7%</t>
+        <v>82</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▲ 9,3%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 645,00</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▲ 313,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 35,2%</t>
+        <v>75</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▲ 2,7%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 156,00</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,9%</t>
+        <v>73</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▲ 35,2%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 83,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>▼ 8,9%</t>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 934,00</t>
+          <t>R$ 156,00</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>▲ 5,7%</t>
+          <t>▼ 8,9%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
+          <t>R$ 934,00</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,7%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 32,5%</t>
+        <v>56</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▲ 5,7%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,14 +1654,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1684,25 +1684,25 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 490,00</t>
+          <t>R$ 467,00</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>▲ 214,1%</t>
+          <t>▼ 4,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▲ 81,8%</t>
+        <v>53</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▲ 32,5%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,14 +1727,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
+          <t>R$ 490,00</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>▼ 51,4%</t>
+          <t>▲ 214,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 15,8%</t>
+        <v>40</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▲ 81,8%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,14 +1800,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 321,00</t>
+          <t>R$ 156,00</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>▲ 99,4%</t>
+          <t>▼ 51,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>▼ 51,3%</t>
+          <t>▲ 15,8%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,14 +1873,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 161,00</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 321,00</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▲ 99,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▲ 85,7%</t>
+          <t>▼ 51,3%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,14 +1946,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -1981,20 +1981,20 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>39</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▲ 85,7%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,14 +2019,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 161,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2067,15 +2067,15 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2133,9 +2133,9 @@
       <c r="I23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2165,14 +2165,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2198,17 +2198,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 95,7%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2238,14 +2238,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 482,00</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 67,6%</t>
+        <v>1</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▼ 95,7%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,14 +2311,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 803,00</t>
+          <t>R$ 482,00</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,6%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▲ 7,6%</t>
+          <t>▼ 67,6%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,14 +2384,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 482,00</t>
+          <t>R$ 803,00</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,9%</t>
+          <t>▲ 66,6%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 37,5%</t>
+        <v>71</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▲ 7,6%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,14 +2457,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2487,25 +2487,25 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 642,00</t>
+          <t>R$ 482,00</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>▲ 298,8%</t>
+          <t>▼ 24,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,0%</t>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,14 +2530,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 161,00</t>
+          <t>R$ 642,00</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>▼ 85,7%</t>
+          <t>▲ 298,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>▲ 48,5%</t>
+          <t>▼ 2,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,14 +2603,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2633,33 +2633,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.124,00</t>
+          <t>R$ 161,00</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>▲ 40,0%</t>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,9%</t>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,14 +2676,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2706,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 803,00</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,2%</t>
+          <t>R$ 1.124,00</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 17,1%</t>
+        <v>33</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▼ 2,9%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,14 +2749,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2779,33 +2779,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 321,00</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 99,4%</t>
+          <t>R$ 803,00</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▲ 150,2%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,6%</t>
+        <v>34</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▼ 17,1%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,14 +2822,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2852,33 +2852,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 161,00</t>
+          <t>R$ 321,00</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>▼ 49,8%</t>
+          <t>▲ 99,4%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>▲ 43,2%</t>
+          <t>▼ 22,6%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,14 +2895,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2925,33 +2925,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 321,00</t>
+          <t>R$ 161,00</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>▲ 99,4%</t>
+          <t>▼ 49,8%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 54,2%</t>
+        <v>53</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▲ 43,2%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,14 +2968,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 161,00</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 321,00</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>▲ 99,4%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▲ 166,7%</t>
+        <v>37</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▲ 54,2%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,14 +3041,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3071,33 +3071,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 161,00</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▼ 59,1%</t>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,14 +3114,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3144,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 482,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>▲ 199,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>▲ 37,5%</t>
+          <t>▼ 59,1%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,14 +3187,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3217,33 +3217,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 161,00</t>
+          <t>R$ 482,00</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>▼ 49,8%</t>
+          <t>▲ 199,4%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,8%</t>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,14 +3260,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3290,25 +3290,25 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 321,00</t>
+          <t>R$ 161,00</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>▲ 80,3%</t>
+          <t>▼ 49,8%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,5%</t>
+        <v>16</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,8%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,14 +3333,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3363,25 +3363,25 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 178,00</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 321,00</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▲ 80,3%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>▲ 110,0%</t>
+          <t>▼ 9,5%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,14 +3406,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3441,20 +3441,20 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>21</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▲ 110,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
@@ -3479,14 +3479,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3509,33 +3509,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 178,00</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3552,14 +3552,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3582,33 +3582,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 357,00</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,14 +3625,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 357,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3664,24 +3664,24 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1500,0%</t>
+        <v>32</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3698,14 +3698,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3737,11 +3737,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>16</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1500,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3771,14 +3771,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3809,10 +3809,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I46" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3821,39 +3819,37 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3925,12 +3921,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4002,12 +3998,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4079,12 +4075,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4156,12 +4152,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4233,12 +4229,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4310,12 +4306,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4387,12 +4383,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4464,12 +4460,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4541,12 +4537,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4618,12 +4614,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4695,12 +4691,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4772,12 +4768,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4849,12 +4845,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4926,12 +4922,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5003,12 +4999,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5080,14 +5076,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5110,7 +5106,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5118,8 +5114,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
-        <v>0</v>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5128,39 +5126,41 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5186,17 +5186,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5226,14 +5226,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5256,33 +5256,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 459,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 68,9%</t>
+        <v>0</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5299,14 +5299,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5329,33 +5329,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 459,00</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>▲ 246,2%</t>
+          <t>▼ 68,9%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5372,14 +5372,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5407,20 +5407,20 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>45</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▲ 246,2%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5445,14 +5445,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 306,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5483,10 +5483,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I68" s="2" t="n">
+        <v>13</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5495,39 +5493,37 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>15,4%</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5599,14 +5595,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5629,7 +5625,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5637,8 +5633,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="2" t="n">
-        <v>0</v>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5647,39 +5645,41 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5705,17 +5705,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5745,14 +5745,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5775,33 +5775,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 153,00</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5818,14 +5818,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5848,33 +5848,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 153,00</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>▲ 53,8%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5891,14 +5891,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5921,33 +5921,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 360,00</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>40</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▲ 53,8%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5964,14 +5964,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -5994,33 +5994,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 360,00</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>26</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -6037,14 +6037,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -6067,33 +6067,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>▲ 73,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6110,14 +6110,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -6140,33 +6140,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 306,00</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▲ 36,4%</t>
+        <v>26</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6183,14 +6183,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -6213,33 +6213,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 153,00</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
+        <v>15</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▲ 36,4%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6256,14 +6256,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -6286,33 +6286,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 153,00</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>▼ 52,6%</t>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6329,14 +6329,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -6359,33 +6359,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>9</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 52,6%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6402,14 +6402,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -6437,15 +6437,15 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▲ 35,7%</t>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6475,14 +6475,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -6505,33 +6505,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 277,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 55,6%</t>
+        <v>19</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▲ 35,7%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6548,14 +6548,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -6578,33 +6578,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▲ 55,6%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6621,14 +6621,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -6651,33 +6651,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 277,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,1%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6694,14 +6694,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -6724,33 +6724,33 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 139,00</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>▲ 7,7%</t>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6767,14 +6767,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-029</t>
@@ -6802,20 +6802,20 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 30,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▲ 7,7%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6840,78 +6840,151 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 139,00</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▲ 30,0%</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>UTD-029</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>Kit 6 Potes 1L vittaza</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>6482775916</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>R$ 178,35</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="n">
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr">
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L87" s="2" t="n">
+      <c r="L88" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M87" s="2" t="inlineStr">
+      <c r="M88" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="N87" s="2" t="inlineStr">
+      <c r="N88" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O87" s="2" t="inlineStr">
+      <c r="O88" s="2" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O87"/>
+  <autoFilter ref="A1:O88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-029-KIT-6-POTES-1L-VITTAZA.xlsx
+++ b/saida_skus/SKU_UTD-029-KIT-6-POTES-1L-VITTAZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$92</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O88"/>
+  <dimension ref="A1:O92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 623,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▲ 9,1%</t>
+          <t>▼ 19,1%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -667,20 +667,20 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>▼ 6,9%</t>
+          <t>▲ 99,4%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>▼ 21,4%</t>
+        <v>47</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
@@ -688,7 +688,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 334,00</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 156,00</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 467,00</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▼ 37,3%</t>
+        <v>36</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 645,00</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▲ 93,1%</t>
+          <t>R$ 623,00</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▲ 26,4%</t>
+        <v>36</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,1%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,25 +954,25 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 334,00</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 311,00</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>33</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1030,22 +1030,22 @@
           <t>R$ 334,00</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>▲ 7,4%</t>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>42</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 311,00</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,4%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>▲ 13,3%</t>
+          <t>▼ 37,3%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,2%</t>
+          <t>R$ 645,00</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 93,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>▼ 26,8%</t>
+          <t>▲ 26,4%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,25 +1246,25 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 311,00</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>▼ 51,8%</t>
+          <t>R$ 334,00</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▲ 9,3%</t>
+        <v>53</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 645,00</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▲ 313,5%</t>
+          <t>R$ 334,00</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>▲ 2,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 311,00</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▲ 35,2%</t>
+        <v>68</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 13,3%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 467,00</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 50,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>▲ 5,9%</t>
+          <t>▼ 26,8%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>▼ 83,3%</t>
+          <t>R$ 311,00</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 51,8%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>▼ 8,9%</t>
+          <t>▲ 9,3%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 934,00</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 645,00</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 313,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▲ 5,7%</t>
+        <v>75</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2,7%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>▼ 4,7%</t>
+          <t>R$ 156,00</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▲ 32,5%</t>
+        <v>73</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▲ 35,2%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 490,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>▲ 214,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▲ 81,8%</t>
+        <v>54</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1833,22 +1833,22 @@
           <t>R$ 156,00</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>▼ 51,4%</t>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>▲ 15,8%</t>
+          <t>▼ 8,9%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 321,00</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▲ 99,4%</t>
+          <t>R$ 934,00</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▼ 51,3%</t>
+          <t>▲ 5,7%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 161,00</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 467,00</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,7%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▲ 85,7%</t>
+        <v>53</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 32,5%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 161,00</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 490,00</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 214,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>40</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 81,8%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 156,00</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 51,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>22</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,8%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 321,00</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>19</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 51,3%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 161,00</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▲ 85,7%</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▼ 95,7%</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 482,00</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+          <t>R$ 161,00</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▼ 67,6%</t>
+        <v>21</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 803,00</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>▲ 66,6%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▲ 7,6%</t>
+        <v>0</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2487,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 482,00</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>▼ 24,9%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▲ 37,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 642,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>▲ 298,8%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▼ 2,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 95,7%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2633,33 +2633,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 161,00</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 85,7%</t>
+          <t>R$ 482,00</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>▲ 48,5%</t>
+          <t>▼ 67,6%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2706,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.124,00</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+          <t>R$ 803,00</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,6%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>▼ 2,9%</t>
+          <t>▲ 7,6%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2779,33 +2779,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 803,00</t>
+          <t>R$ 482,00</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>▲ 150,2%</t>
+          <t>▼ 24,9%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>▼ 17,1%</t>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2852,33 +2852,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 321,00</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>▲ 99,4%</t>
+          <t>R$ 642,00</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>▲ 298,8%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▼ 22,6%</t>
+        <v>48</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2928,22 +2928,22 @@
           <t>R$ 161,00</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>▼ 49,8%</t>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▲ 43,2%</t>
+        <v>49</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 321,00</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>▲ 99,4%</t>
+          <t>R$ 1.124,00</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>▲ 54,2%</t>
+          <t>▼ 2,9%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3071,33 +3071,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 161,00</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 803,00</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,2%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▲ 166,7%</t>
+          <t>▼ 17,1%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3144,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 321,00</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 99,4%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▼ 59,1%</t>
+        <v>41</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,6%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3217,33 +3217,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 482,00</t>
+          <t>R$ 161,00</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>▲ 199,4%</t>
+          <t>▼ 49,8%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▲ 37,5%</t>
+        <v>53</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 43,2%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3290,33 +3290,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 161,00</t>
+          <t>R$ 321,00</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>▼ 49,8%</t>
+          <t>▲ 99,4%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,8%</t>
+          <t>▲ 54,2%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3363,25 +3363,25 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 321,00</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▲ 80,3%</t>
+          <t>R$ 161,00</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>▼ 9,5%</t>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3436,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 178,00</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>▲ 110,0%</t>
+          <t>▼ 59,1%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3509,33 +3509,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 178,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 482,00</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 199,4%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>22</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3582,33 +3582,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 161,00</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,8%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,8%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3655,33 +3655,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 357,00</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 321,00</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 80,3%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 9,5%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3728,33 +3728,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 178,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▲ 1500,0%</t>
+        <v>21</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▲ 110,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 178,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3810,24 +3810,24 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3874,59 +3874,55 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3951,7 +3947,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 357,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3959,51 +3955,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I48" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>6,3%</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4028,7 +4020,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4036,51 +4028,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I49" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1500,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4105,7 +4093,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4113,10 +4101,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I50" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4125,39 +4111,37 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4229,12 +4213,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4306,12 +4290,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4383,12 +4367,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4460,12 +4444,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4537,12 +4521,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4614,12 +4598,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4691,12 +4675,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4768,12 +4752,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4845,12 +4829,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4922,12 +4906,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4999,12 +4983,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5076,12 +5060,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5153,12 +5137,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5183,7 +5167,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5191,8 +5175,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="n">
-        <v>0</v>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5201,37 +5187,39 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5256,55 +5244,59 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5329,55 +5321,59 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 459,00</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▼ 68,9%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="n">
-        <v>3</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5402,55 +5398,59 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▲ 246,2%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5484,7 +5484,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5493,15 +5493,15 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5518,12 +5518,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5548,59 +5548,55 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5625,59 +5621,55 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 459,00</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 68,9%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>21,4%</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5702,33 +5694,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 306,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>45</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▲ 246,2%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5745,12 +5737,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5775,33 +5767,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 306,00</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5818,12 +5810,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5848,7 +5840,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 153,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5856,47 +5848,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5921,55 +5917,59 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▲ 53,8%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 360,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6012,15 +6012,15 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6070,7 +6070,7 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H76" s="4" t="inlineStr">
+      <c r="H76" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -6078,7 +6078,7 @@
       <c r="I76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J76" s="4" t="inlineStr">
+      <c r="J76" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -6110,12 +6110,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 306,00</t>
+          <t>R$ 153,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6149,24 +6149,24 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>▲ 73,3%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6216,17 +6216,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H78" s="4" t="inlineStr">
+      <c r="H78" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▲ 36,4%</t>
+        <v>40</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 53,8%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 153,00</t>
+          <t>R$ 360,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6295,16 +6295,16 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
+        <v>26</v>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6329,12 +6329,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6362,17 +6362,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H80" s="4" t="inlineStr">
+      <c r="H80" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▼ 52,6%</t>
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6402,12 +6402,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6432,25 +6432,25 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
+          <t>R$ 306,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>26</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6505,33 +6505,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▲ 35,7%</t>
+        <v>15</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 36,4%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6578,33 +6578,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H83" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 153,00</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▲ 55,6%</t>
+        <v>11</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6651,12 +6651,12 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
@@ -6664,20 +6664,20 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 52,6%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6694,12 +6694,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6724,33 +6724,33 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H85" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 277,00</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+        <v>19</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6767,12 +6767,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6797,33 +6797,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 139,00</t>
+          <t>R$ 277,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▲ 7,7%</t>
+        <v>19</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 35,7%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6870,33 +6870,33 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 139,00</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▲ 30,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>▲ 55,6%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6913,78 +6913,370 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 277,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 139,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,7%</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 139,00</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>▲ 30,0%</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>UTD-029</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>Kit 6 Potes 1L vittaza</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>6482775916</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>R$ 178,35</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>UTD-029</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Kit 6 Potes 1L vittaza</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>6482775916</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 178,35</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="n">
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K88" s="2" t="inlineStr">
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L88" s="2" t="n">
+      <c r="L92" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M88" s="2" t="inlineStr">
+      <c r="M92" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="N88" s="2" t="inlineStr">
+      <c r="N92" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O88" s="2" t="inlineStr">
+      <c r="O92" s="2" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O88"/>
+  <autoFilter ref="A1:O92"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>